--- a/docs/Files/ODYM_Tutorial6_EoLRecoveryRateLL_V1.0.xlsx
+++ b/docs/Files/ODYM_Tutorial6_EoLRecoveryRateLL_V1.0.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F282C1-1EEB-4FAE-A7B3-410CBCD2246D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A8F294-4C16-4DA4-A487-0A98D50ADE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="110">
   <si>
     <t>Format_Version</t>
   </si>
@@ -201,12 +201,6 @@
     <t>none</t>
   </si>
   <si>
-    <t>Automotive steel</t>
-  </si>
-  <si>
-    <t>Steel shred</t>
-  </si>
-  <si>
     <t>ODYM_Tutorial6_EoLRecoveryRate</t>
   </si>
   <si>
@@ -222,30 +216,9 @@
     <t>BAU</t>
   </si>
   <si>
-    <t>Efficient</t>
-  </si>
-  <si>
     <t>Scenario</t>
   </si>
   <si>
-    <t>vehicles</t>
-  </si>
-  <si>
-    <t>machinery</t>
-  </si>
-  <si>
-    <t>construction</t>
-  </si>
-  <si>
-    <t>products and other</t>
-  </si>
-  <si>
-    <t>Construction grade steel</t>
-  </si>
-  <si>
-    <t>Heavy melt, plate, and structural steel scrap</t>
-  </si>
-  <si>
     <t>Recovery rate</t>
   </si>
   <si>
@@ -367,12 +340,6 @@
   </si>
   <si>
     <t>From dataset 4_PY_WorldSteel_EoL_RR_SteelScrap, 2007 value</t>
-  </si>
-  <si>
-    <t>From dataset 4_PY_WorldSteel_EoL_RR_SteelScrap, 2007 value, ca. average of containers and appliances</t>
-  </si>
-  <si>
-    <t>From dataset 4_PY_WorldSteel_EoL_RR_SteelScrap, 2050 value</t>
   </si>
   <si>
     <t>ODYM_Classifications_LL</t>
@@ -850,7 +817,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
@@ -864,7 +831,7 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
@@ -920,7 +887,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
@@ -934,7 +901,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>16</v>
@@ -948,7 +915,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>16</v>
@@ -1018,7 +985,7 @@
         <v>36</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
@@ -1096,16 +1063,16 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>16</v>
@@ -1116,16 +1083,16 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>16</v>
@@ -1136,16 +1103,16 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>16</v>
@@ -1156,10 +1123,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>14</v>
@@ -1197,7 +1164,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="23.36328125" customWidth="1"/>
@@ -1214,16 +1181,16 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>11</v>
@@ -1243,19 +1210,19 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="E2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1267,24 +1234,24 @@
         <v>55</v>
       </c>
       <c r="I2" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1296,188 +1263,14 @@
         <v>55</v>
       </c>
       <c r="I3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" t="s">
-        <v>55</v>
-      </c>
-      <c r="I7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I9" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D10" s="1"/>
-    </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F35" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="29" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F29" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1491,40 +1284,40 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
@@ -1536,13 +1329,13 @@
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G3" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="H3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1557,61 +1350,61 @@
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="P3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Files/ODYM_Tutorial6_EoLRecoveryRateLL_V1.0.xlsx
+++ b/docs/Files/ODYM_Tutorial6_EoLRecoveryRateLL_V1.0.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A8F294-4C16-4DA4-A487-0A98D50ADE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C769219-D9A5-4CF0-BDE8-DACBEAE8E2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1222,7 +1222,7 @@
         <v>108</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1251,7 +1251,7 @@
         <v>109</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F3">
         <v>1</v>
